--- a/data/trans_bre/MCS12_SP_R3-Edad-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R3-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 11,0</t>
+          <t>2,24; 11,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 7,14</t>
+          <t>-2,85; 7,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 5,89</t>
+          <t>-2,96; 6,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,0; 20,85</t>
+          <t>5,15; 20,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,39; 112,36</t>
+          <t>15,7; 115,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 54,01</t>
+          <t>-15,78; 56,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 62,53</t>
+          <t>-23,03; 70,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43,05; 463,88</t>
+          <t>28,31; 422,95</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 12,78</t>
+          <t>4,55; 12,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 10,36</t>
+          <t>0,75; 9,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 6,38</t>
+          <t>-1,99; 6,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 11,42</t>
+          <t>-1,95; 11,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,67; 110,89</t>
+          <t>30,0; 111,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 66,54</t>
+          <t>3,51; 63,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 46,35</t>
+          <t>-11,71; 49,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 114,79</t>
+          <t>-13,43; 126,97</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 8,59</t>
+          <t>-0,5; 8,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 15,36</t>
+          <t>5,26; 15,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 9,44</t>
+          <t>0,57; 9,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 6,46</t>
+          <t>-3,02; 6,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 45,7</t>
+          <t>-2,56; 44,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,99; 74,85</t>
+          <t>21,06; 75,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 59,39</t>
+          <t>2,39; 60,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 40,74</t>
+          <t>-14,06; 40,44</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,94; 19,0</t>
+          <t>8,54; 19,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 18,09</t>
+          <t>7,82; 18,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 12,39</t>
+          <t>2,66; 12,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 19,38</t>
+          <t>1,0; 20,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,69; 130,85</t>
+          <t>42,49; 133,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,84; 91,06</t>
+          <t>31,11; 95,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 59,02</t>
+          <t>9,93; 58,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,52; 279,04</t>
+          <t>4,26; 302,02</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 13,89</t>
+          <t>1,78; 14,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 19,44</t>
+          <t>6,93; 18,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,77; 17,98</t>
+          <t>6,36; 17,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 11,82</t>
+          <t>2,75; 11,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,83; 62,94</t>
+          <t>5,29; 67,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,89; 85,09</t>
+          <t>24,01; 81,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,86; 97,7</t>
+          <t>25,87; 94,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,63; 55,79</t>
+          <t>10,22; 54,91</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 10,41</t>
+          <t>-3,17; 10,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,38; 18,87</t>
+          <t>4,41; 18,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,49; 23,13</t>
+          <t>10,31; 23,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,4; 56,56</t>
+          <t>4,82; 58,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 44,4</t>
+          <t>-10,88; 47,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,98; 88,01</t>
+          <t>14,9; 88,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,85; 150,16</t>
+          <t>48,08; 155,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,45; 269,94</t>
+          <t>18,5; 271,96</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 12,47</t>
+          <t>-2,28; 13,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,84; 22,31</t>
+          <t>6,15; 21,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,25; 18,51</t>
+          <t>2,56; 17,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,53; 17,06</t>
+          <t>6,17; 17,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 55,28</t>
+          <t>-7,41; 60,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,03; 83,76</t>
+          <t>16,62; 82,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,96; 74,68</t>
+          <t>7,2; 73,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,03; 62,64</t>
+          <t>17,8; 61,09</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,95</t>
+          <t>5,94; 9,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,28; 12,78</t>
+          <t>8,09; 12,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,97; 9,96</t>
+          <t>6,11; 10,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,09; 23,94</t>
+          <t>7,16; 25,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,56; 56,06</t>
+          <t>29,99; 56,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,85; 60,67</t>
+          <t>34,81; 59,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,23; 56,19</t>
+          <t>30,0; 55,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,82; 140,26</t>
+          <t>35,98; 160,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/MCS12_SP_R3-Edad-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R3-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,4</t>
+          <t>11,61</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>176,96%</t>
+          <t>131,0%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 11,12</t>
+          <t>2,19; 10,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 7,45</t>
+          <t>-3,14; 7,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 6,5</t>
+          <t>-3,13; 5,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 20,7</t>
+          <t>4,45; 18,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,7; 115,57</t>
+          <t>12,34; 106,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 56,26</t>
+          <t>-16,78; 51,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 70,4</t>
+          <t>-24,6; 66,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,31; 422,95</t>
+          <t>30,43; 330,25</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,95</t>
+          <t>7,44</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>58,04%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 12,77</t>
+          <t>4,3; 12,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 9,93</t>
+          <t>0,55; 9,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 6,59</t>
+          <t>-2,05; 6,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 11,61</t>
+          <t>2,07; 13,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,0; 111,5</t>
+          <t>26,66; 107,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 63,31</t>
+          <t>3,19; 63,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 49,67</t>
+          <t>-13,35; 51,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 126,97</t>
+          <t>10,15; 132,49</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>3,88</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 8,22</t>
+          <t>-0,7; 8,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,26; 15,19</t>
+          <t>5,53; 15,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 9,26</t>
+          <t>0,25; 8,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 6,25</t>
+          <t>-0,26; 8,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 44,19</t>
+          <t>-3,61; 44,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,06; 75,23</t>
+          <t>20,84; 73,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 60,37</t>
+          <t>1,2; 56,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 40,44</t>
+          <t>-1,61; 56,04</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,21</t>
+          <t>5,42</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,54; 19,2</t>
+          <t>8,76; 19,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 18,4</t>
+          <t>7,79; 18,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 12,13</t>
+          <t>2,02; 12,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 20,69</t>
+          <t>1,26; 9,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,49; 133,97</t>
+          <t>45,67; 132,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,11; 95,47</t>
+          <t>29,65; 92,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 58,87</t>
+          <t>7,28; 61,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 302,02</t>
+          <t>5,28; 50,32</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>7,97</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 14,71</t>
+          <t>1,48; 14,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,93; 18,87</t>
+          <t>6,61; 19,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 17,97</t>
+          <t>6,16; 18,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 11,66</t>
+          <t>3,65; 12,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,29; 67,72</t>
+          <t>6,05; 64,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,01; 81,52</t>
+          <t>21,35; 83,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,87; 94,97</t>
+          <t>25,37; 101,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,22; 54,91</t>
+          <t>14,17; 58,44</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29,58</t>
+          <t>7,56</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>119,25%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 10,84</t>
+          <t>-3,15; 10,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,41; 18,58</t>
+          <t>3,79; 18,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,31; 23,03</t>
+          <t>9,76; 23,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,82; 58,01</t>
+          <t>2,49; 12,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 47,36</t>
+          <t>-10,58; 44,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,9; 88,86</t>
+          <t>12,41; 85,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,08; 155,95</t>
+          <t>43,41; 155,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,5; 271,96</t>
+          <t>9,09; 57,2</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,76</t>
+          <t>11,65</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,54%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 13,38</t>
+          <t>-3,13; 13,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,15; 21,9</t>
+          <t>6,47; 22,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 17,92</t>
+          <t>2,12; 18,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,17; 17,17</t>
+          <t>5,96; 17,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 60,75</t>
+          <t>-9,56; 61,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,62; 82,27</t>
+          <t>17,17; 84,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,2; 73,68</t>
+          <t>6,35; 73,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,8; 61,09</t>
+          <t>17,09; 59,92</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12,55</t>
+          <t>8,11</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>41,26%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,94; 9,87</t>
+          <t>5,82; 9,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,09; 12,55</t>
+          <t>8,43; 12,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,13</t>
+          <t>5,87; 9,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,16; 25,9</t>
+          <t>6,25; 10,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,99; 56,25</t>
+          <t>29,39; 56,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,81; 59,19</t>
+          <t>35,6; 59,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,0; 55,94</t>
+          <t>29,06; 54,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,98; 160,34</t>
+          <t>30,02; 54,01</t>
         </is>
       </c>
     </row>
